--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R10" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R11" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>78940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R13" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,26 +2013,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2053,7 +2033,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B15" t="n">
-        <v>78937</v>
+        <v>80288</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R15" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,6 +2225,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78938</v>
+        <v>78941</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,31 +2633,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2665,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R19" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,6 +2709,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,22 +2720,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2757,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,26 +2759,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2795,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R20" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,7 +2840,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2855,17 +2850,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B10" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R10" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B11" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R11" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B13" t="n">
-        <v>78940</v>
+        <v>80314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,6 +2013,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,7 +2053,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B15" t="n">
-        <v>80288</v>
+        <v>78966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R15" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,26 +2245,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v>130446091</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,26 +2633,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R19" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,7 +2714,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2720,17 +2724,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2748,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,31 +2768,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2791,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R20" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,6 +2844,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2850,22 +2855,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,31 +2633,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2665,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R19" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,6 +2709,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,22 +2720,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2757,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,26 +2759,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2795,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R20" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,7 +2840,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2855,17 +2850,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B10" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R10" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R11" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B13" t="n">
-        <v>80314</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R13" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,26 +2013,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2053,7 +2033,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B15" t="n">
-        <v>78966</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R15" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,6 +2225,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v>130446091</v>
       </c>
       <c r="B16" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B10" t="n">
         <v>78968</v>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R10" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B11" t="n">
         <v>78968</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R11" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>80316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,6 +2013,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2136,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R15" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,26 +2245,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,26 +2633,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R19" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,7 +2714,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2720,17 +2724,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2748,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,31 +2768,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2791,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R20" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,6 +2844,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2850,22 +2855,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B13" t="n">
-        <v>80316</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R13" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,26 +2013,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2050,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130446105</v>
+        <v>130446094</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>80316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,21 +2041,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2088,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510281</v>
+        <v>510303</v>
       </c>
       <c r="R14" t="n">
-        <v>6956033</v>
+        <v>6956049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,6 +2119,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446106</v>
+        <v>130446105</v>
       </c>
       <c r="B15" t="n">
         <v>78968</v>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510310</v>
+        <v>510281</v>
       </c>
       <c r="R15" t="n">
-        <v>6956051</v>
+        <v>6956033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B10" t="n">
         <v>78968</v>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R10" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B11" t="n">
         <v>78968</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R11" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130446094</v>
+        <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>80316</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,21 +2041,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510303</v>
+        <v>510281</v>
       </c>
       <c r="R14" t="n">
-        <v>6956049</v>
+        <v>6956033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,26 +2119,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2156,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446105</v>
+        <v>130446094</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>80316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510281</v>
+        <v>510303</v>
       </c>
       <c r="R15" t="n">
-        <v>6956033</v>
+        <v>6956049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,6 +2225,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,31 +2633,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2665,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R19" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,6 +2709,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,22 +2720,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2757,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2768,26 +2759,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2795,10 +2791,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R20" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,7 +2840,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2855,17 +2850,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130446107</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>130446101</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>130446106</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78976</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>130446094</v>
       </c>
       <c r="B15" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>130446091</v>
       </c>
       <c r="B16" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78969</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B10" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R10" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B11" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R11" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B13" t="n">
-        <v>78976</v>
+        <v>80325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R13" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,6 +2013,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2033,7 +2053,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78976</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B15" t="n">
-        <v>80324</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2194,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R15" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,26 +2245,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2265,7 +2265,7 @@
         <v>130446091</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>130446095</v>
       </c>
       <c r="B5" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>130446096</v>
       </c>
       <c r="B6" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>130446108</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>130446112</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>130446104</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>130446101</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>130446107</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>130446097</v>
       </c>
       <c r="B12" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>130446094</v>
       </c>
       <c r="B13" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>130446105</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>130446106</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78978</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>130446091</v>
       </c>
       <c r="B16" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>130446093</v>
       </c>
       <c r="B17" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>130446092</v>
       </c>
       <c r="B18" t="n">
-        <v>78978</v>
+        <v>78979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>130446111</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>130446090</v>
       </c>
       <c r="B20" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -1581,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446101</v>
+        <v>130446107</v>
       </c>
       <c r="B10" t="n">
         <v>78978</v>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510076</v>
+        <v>510330</v>
       </c>
       <c r="R10" t="n">
-        <v>6956239</v>
+        <v>6956090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446107</v>
+        <v>130446101</v>
       </c>
       <c r="B11" t="n">
         <v>78978</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510330</v>
+        <v>510076</v>
       </c>
       <c r="R11" t="n">
-        <v>6956090</v>
+        <v>6956239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446094</v>
+        <v>130446106</v>
       </c>
       <c r="B13" t="n">
-        <v>80326</v>
+        <v>78978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510303</v>
+        <v>510310</v>
       </c>
       <c r="R13" t="n">
-        <v>6956049</v>
+        <v>6956051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,26 +2013,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2156,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446106</v>
+        <v>130446094</v>
       </c>
       <c r="B15" t="n">
-        <v>78978</v>
+        <v>80326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510310</v>
+        <v>510303</v>
       </c>
       <c r="R15" t="n">
-        <v>6956051</v>
+        <v>6956049</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,6 +2225,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446111</v>
+        <v>130446090</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,26 +2633,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2660,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509946</v>
+        <v>510264</v>
       </c>
       <c r="R19" t="n">
-        <v>6956346</v>
+        <v>6956227</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2705,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, på tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2709,7 +2714,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2720,17 +2724,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2748,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446090</v>
+        <v>130446111</v>
       </c>
       <c r="B20" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,31 +2768,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2791,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510264</v>
+        <v>509946</v>
       </c>
       <c r="R20" t="n">
-        <v>6956227</v>
+        <v>6956346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,6 +2844,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2850,22 +2855,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>343973</v>
+        <v>132842</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510267.3744402934</v>
+        <v>510269</v>
       </c>
       <c r="R2" t="n">
-        <v>6956137.917625297</v>
+        <v>6956138</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132842</v>
+        <v>343973</v>
       </c>
       <c r="B3" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510269.2109588626</v>
+        <v>510267</v>
       </c>
       <c r="R3" t="n">
-        <v>6956137.923349549</v>
+        <v>6956138</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +872,7 @@
         <v>712642</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510313.5371488811</v>
+        <v>510314</v>
       </c>
       <c r="R4" t="n">
-        <v>6956058.28434818</v>
+        <v>6956058</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130446095</v>
+        <v>130446110</v>
       </c>
       <c r="B5" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1004,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510330</v>
+        <v>509881</v>
       </c>
       <c r="R5" t="n">
-        <v>6956057</v>
+        <v>6956321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1042,11 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1100,6 +1060,21 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1117,32 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130446096</v>
+        <v>130446111</v>
       </c>
       <c r="B6" t="n">
-        <v>80340</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1155,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510319</v>
+        <v>509946</v>
       </c>
       <c r="R6" t="n">
-        <v>6956041</v>
+        <v>6956346</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,6 +1168,11 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1210,22 +1190,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1243,32 +1218,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130446108</v>
+        <v>130446112</v>
       </c>
       <c r="B7" t="n">
-        <v>78992</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510311</v>
+        <v>510321</v>
       </c>
       <c r="R7" t="n">
-        <v>6956186</v>
+        <v>6956057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,6 +1294,11 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Garnlav på tall.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1332,6 +1312,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1349,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130446112</v>
+        <v>80555282</v>
       </c>
       <c r="B8" t="n">
-        <v>79235</v>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,40 +1355,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörmyren Öst, Jmt</t>
+          <t>Norra Sverige, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510321</v>
+        <v>510218</v>
       </c>
       <c r="R8" t="n">
-        <v>6956057</v>
+        <v>6956032</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,17 +1409,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav på tall.</t>
+          <t>2019-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,49 +1433,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130446104</v>
+        <v>130448977</v>
       </c>
       <c r="B9" t="n">
-        <v>78992</v>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510251</v>
+        <v>510238</v>
       </c>
       <c r="R9" t="n">
-        <v>6956230</v>
+        <v>6956067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,12 +1519,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,6 +1540,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1581,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130446107</v>
+        <v>1981490</v>
       </c>
       <c r="B10" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,22 +1601,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörmyren Öst, Jmt</t>
+          <t>Sidsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510330</v>
+        <v>510342</v>
       </c>
       <c r="R10" t="n">
-        <v>6956090</v>
+        <v>6956099</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-11-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-11-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,34 +1651,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Sebastian Acker</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130446101</v>
+        <v>130446098</v>
       </c>
       <c r="B11" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510076</v>
+        <v>509854</v>
       </c>
       <c r="R11" t="n">
-        <v>6956239</v>
+        <v>6956341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130446097</v>
+        <v>130446101</v>
       </c>
       <c r="B12" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1831,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510322</v>
+        <v>510076</v>
       </c>
       <c r="R12" t="n">
-        <v>6956046</v>
+        <v>6956239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,11 +1851,6 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1887,26 +1864,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1924,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130446106</v>
+        <v>130446102</v>
       </c>
       <c r="B13" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510310</v>
+        <v>510080</v>
       </c>
       <c r="R13" t="n">
-        <v>6956051</v>
+        <v>6956202</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130446105</v>
+        <v>130446103</v>
       </c>
       <c r="B14" t="n">
-        <v>78992</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510281</v>
+        <v>510124</v>
       </c>
       <c r="R14" t="n">
-        <v>6956033</v>
+        <v>6956199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,10 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130446094</v>
+        <v>130446104</v>
       </c>
       <c r="B15" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2104,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510303</v>
+        <v>510251</v>
       </c>
       <c r="R15" t="n">
-        <v>6956049</v>
+        <v>6956230</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,26 +2182,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2262,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130446091</v>
+        <v>130446105</v>
       </c>
       <c r="B16" t="n">
-        <v>58037</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,50 +2210,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörmyren Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510310</v>
+        <v>510281</v>
       </c>
       <c r="R16" t="n">
-        <v>6956164</v>
+        <v>6956033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,17 +2275,13 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2385,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130446093</v>
+        <v>130446106</v>
       </c>
       <c r="B17" t="n">
-        <v>80340</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2423,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510315</v>
+        <v>510310</v>
       </c>
       <c r="R17" t="n">
-        <v>6956028</v>
+        <v>6956051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,11 +2381,6 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en stående död sälg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2479,26 +2394,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2516,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130446092</v>
+        <v>130446107</v>
       </c>
       <c r="B18" t="n">
-        <v>78993</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,21 +2422,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2622,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130446111</v>
+        <v>130446108</v>
       </c>
       <c r="B19" t="n">
-        <v>79235</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2555,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509946</v>
+        <v>510311</v>
       </c>
       <c r="R19" t="n">
-        <v>6956346</v>
+        <v>6956186</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,11 +2593,6 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2716,21 +2606,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2748,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130446090</v>
+        <v>130448983</v>
       </c>
       <c r="B20" t="n">
-        <v>57878</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,31 +2634,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2791,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510264</v>
+        <v>510086</v>
       </c>
       <c r="R20" t="n">
-        <v>6956227</v>
+        <v>6956190</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,17 +2691,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på tall.</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,32 +2705,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2880,6 +2726,1535 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130448984</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>510208</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6956132</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130448985</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>510207</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6956130</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130446093</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>510315</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6956028</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130446094</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>510303</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6956049</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130446095</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>510330</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6956057</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130446096</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>510319</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6956041</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130446097</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>510322</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6956046</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130446090</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>510264</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6956227</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130446091</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>510310</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6956164</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i ett skogsbestånd som bitvis är flerskiktat och hyser björkhögstubbar.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130446092</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>510330</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6956090</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130446089</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>509854</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6956342</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130448979</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>509857</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6956348</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130448982</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Rörmyren Öst, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>510029</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6956233</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59052-2025 artfynd.xlsx
+++ b/artfynd/A 59052-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/343973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/712642</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446110</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446111</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446112</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80555282</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448977</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,6 +1822,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446098</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446101</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446102</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2090,6 +2155,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446103</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2196,6 +2266,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446104</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446105</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446106</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446107</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2620,6 +2710,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446108</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2726,6 +2821,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448983</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2832,6 +2932,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448984</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,6 +3043,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448985</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3069,6 +3179,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446093</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3195,6 +3310,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446094</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3301,6 +3421,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446095</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446096</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3558,6 +3688,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446097</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3693,6 +3828,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446090</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3816,6 +3956,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446091</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3922,6 +4067,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446092</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4028,6 +4178,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130446089</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448979</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4255,8 +4415,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130448982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>